--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-lm-statut.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-fr-lm-statut.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:19:27+00:00</t>
+    <t>2025-10-21T12:36:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
